--- a/output/pdf_financials_xlsx/IMI.xlsx
+++ b/output/pdf_financials_xlsx/IMI.xlsx
@@ -3313,28 +3313,28 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.524113</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.452451</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.772717</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.671974</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.74481</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.900504</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.88009</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.503898</v>
       </c>
     </row>
     <row r="93">
@@ -6690,7 +6690,11 @@
           <t>Share-based payment reserve 19</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -7956,7 +7960,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -8950,7 +8958,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -9624,7 +9636,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -10388,7 +10404,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>3.524113</v>
       </c>

--- a/output/pdf_financials_xlsx/IMI.xlsx
+++ b/output/pdf_financials_xlsx/IMI.xlsx
@@ -759,25 +759,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.033129</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.08036500000000001</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.030311</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.004007</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001681</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008104999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.008817999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-8.106188</v>
+        <v>-8.139317</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-10.610325</v>
+        <v>-10.69069</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.262928</v>
+        <v>-5.293239</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1310,13 +1310,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.861463</v>
+        <v>-2.863144</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.475904</v>
+        <v>-1.484009</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.393544</v>
+        <v>6.384726</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>3.396463</v>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-8.106188</v>
+        <v>-8.139317</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-10.610325</v>
+        <v>-10.69069</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.262928</v>
+        <v>-5.293239</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.861463</v>
+        <v>-2.863144</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.475904</v>
+        <v>-1.484009</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6.416324</v>
+        <v>6.407506</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>3.661477</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-97.25879574182888</v>
+        <v>-97.65628055764256</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-109.4014183186187</v>
+        <v>-110.2300493910106</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-43.15688706582782</v>
+        <v>-43.40544231945324</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-49.53585609678027</v>
+        <v>-49.56495651642529</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-29.50852513955981</v>
+        <v>-29.67057266856992</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>32.7457095385844</v>
+        <v>32.7007068755781</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>16.22547772732872</v>
@@ -1517,10 +1517,10 @@
         <v>0.562165</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.059409</v>
+        <v>0.160924</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.907491</v>
       </c>
     </row>
     <row r="35">
@@ -1579,10 +1579,10 @@
         <v>0.562165</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.059409</v>
+        <v>0.160924</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.907491</v>
       </c>
     </row>
     <row r="37">
@@ -1951,10 +1951,10 @@
         <v>0.335364</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>0.217987</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.982231</v>
+        <v>2.07474</v>
       </c>
     </row>
     <row r="49">
@@ -4344,16 +4344,16 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.131792</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.103372</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.091781</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.093413</v>
       </c>
       <c r="I124" s="1" t="inlineStr">
         <is>
@@ -4377,16 +4377,16 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.131792</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.103372</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.091781</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.093413</v>
       </c>
       <c r="I125" s="1" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12150,7 +12150,11 @@
           <t>Lease repayments</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -14736,7 +14740,11 @@
           <t>Lease repayments</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -20860,7 +20868,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E292" s="5" t="n">
@@ -20908,7 +20916,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -22282,7 +22290,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -23276,7 +23284,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E336" s="5" t="n">

--- a/output/pdf_financials_xlsx/IMI.xlsx
+++ b/output/pdf_financials_xlsx/IMI.xlsx
@@ -3937,22 +3937,22 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.07592</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.012648</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.10801</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.026812</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.095861</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -11862,7 +11862,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -13032,7 +13036,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -15960,7 +15968,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -16984,7 +16996,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E220" s="5" t="n">
         <v>0.07592</v>
       </c>
